--- a/kaist/kmip/template/kmip_gcam_mapping_template.xlsx
+++ b/kaist/kmip/template/kmip_gcam_mapping_template.xlsx
@@ -466,8 +466,6 @@
           <t>Emissions|CO2|Energy</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -488,8 +486,6 @@
           <t>Emissions|CO2|Energy|Supply|Electricity</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -505,9 +501,6 @@
           <t>Emissions|CO2|Energy|Supply|Heat</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -528,8 +521,6 @@
           <t>Emissions|CO2|Energy|Supply|Hydrogen</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -555,7 +546,6 @@
           <t>Emissions|CO2|Energy|Supply|Liquids; Emissions|CO2|Energy|Supply|Fugitive</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -576,8 +566,6 @@
           <t>Emissions|CO2|Energy|Demand|Industry</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -598,8 +586,6 @@
           <t>Emissions|CO2|Energy|Demand|Industry|Chemicals</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -620,8 +606,6 @@
           <t>Emissions|CO2|Energy|Demand|Industry|Iron and Steel</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -637,9 +621,6 @@
           <t>Emissions|CO2|Energy|Demand|Industry|Non-Metallic Minerals</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -660,8 +641,6 @@
           <t>Emissions|CO2|Energy|Demand|Industry|Other Sector</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -682,8 +661,6 @@
           <t>Emissions|CO2|Energy|Demand|Transportation</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -709,7 +686,6 @@
           <t>Emissions|CO2|Energy|Demand|Transportation|Light-Duty Vehicle; Emissions|CO2|Energy|Demand|Transportation|Truck</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -730,8 +706,6 @@
           <t>Emissions|CO2|Energy|Demand|Transportation|Rail</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -752,8 +726,6 @@
           <t>Emissions|CO2|Energy|Demand|Transportation|Domestic Shipping</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -774,8 +746,6 @@
           <t>Emissions|CO2|Energy|Demand|Transportation|Domestic Aviation</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -796,8 +766,6 @@
           <t>Emissions|CO2|Energy|Demand|Residential and Commercial</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -818,8 +786,6 @@
           <t>Emissions|CO2|Energy|Demand|Residential</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -840,8 +806,6 @@
           <t>Emissions|CO2|Energy|Demand|Commercial</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -862,8 +826,6 @@
           <t>Emissions|CO2|Energy|Demand|AFOFI</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -884,8 +846,6 @@
           <t>Emissions|CH4|Energy</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -906,8 +866,6 @@
           <t>Emissions|CH4|Energy|Supply|Electricity</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -923,9 +881,6 @@
           <t>Emissions|CH4|Energy|Supply|Heat</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -946,8 +901,6 @@
           <t>Emissions|CH4|Energy|Supply|Hydrogen</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -963,13 +916,11 @@
           <t>Emissions|CH4|Energy|Supply|Refinery</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Emissions|CH4|Energy|Supply|Liquids; Emissions|CH4|Energy|Supply|Fugitive</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -990,8 +941,6 @@
           <t>Emissions|CH4|Energy|Demand|Industry</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1007,9 +956,6 @@
           <t>Emissions|CH4|Energy|Demand|Industry|Chemicals</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1025,9 +971,6 @@
           <t>Emissions|CH4|Energy|Demand|Industry|Iron and Steel</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1043,9 +986,6 @@
           <t>Emissions|CH4|Energy|Demand|Industry|Non-Metallic Minerals</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1061,9 +1001,6 @@
           <t>Emissions|CH4|Energy|Demand|Industry|Other Sector</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1084,8 +1021,6 @@
           <t>Emissions|CH4|Energy|Demand|Transportation</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1111,7 +1046,6 @@
           <t>Emissions|CH4|Energy|Demand|Transportation|Light-Duty Vehicle; Emissions|CH4|Energy|Demand|Transportation|Truck</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1132,8 +1066,6 @@
           <t>Emissions|CH4|Energy|Demand|Transportation|Rail</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1154,8 +1086,6 @@
           <t>Emissions|CH4|Energy|Demand|Transportation|Domestic Shipping</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1176,8 +1106,6 @@
           <t>Emissions|CH4|Energy|Demand|Transportation|Domestic Aviation</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1198,8 +1126,6 @@
           <t>Emissions|CH4|Energy|Demand|Residential and Commercial</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1220,8 +1146,6 @@
           <t>Emissions|CH4|Energy|Demand|Residential</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1242,8 +1166,6 @@
           <t>Emissions|CH4|Energy|Demand|Commercial</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1264,8 +1186,6 @@
           <t>Emissions|CH4|Energy|Demand|AFOFI</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1286,8 +1206,6 @@
           <t>Emissions|N2O|Energy</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1308,8 +1226,6 @@
           <t>Emissions|N2O|Energy|Supply|Electricity</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1325,9 +1241,6 @@
           <t>Emissions|N2O|Energy|Supply|Heat</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1343,9 +1256,6 @@
           <t>Emissions|N2O|Energy|Supply|Hydrogen</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1361,13 +1271,11 @@
           <t>Emissions|N2O|Energy|Supply|Refinery</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>Emissions|N2O|Energy|Supply|Liquids; Emissions|N2O|Energy|Supply|Fugitive</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1388,8 +1296,6 @@
           <t>Emissions|N2O|Energy|Demand|Industry</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1405,9 +1311,6 @@
           <t>Emissions|N2O|Energy|Demand|Industry|Chemicals</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1423,9 +1326,6 @@
           <t>Emissions|N2O|Energy|Demand|Industry|Iron and Steel</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1441,9 +1341,6 @@
           <t>Emissions|N2O|Energy|Demand|Industry|Non-Metallic Minerals</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1459,9 +1356,6 @@
           <t>Emissions|N2O|Energy|Demand|Industry|Other Sector</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1482,8 +1376,6 @@
           <t>Emissions|N2O|Energy|Demand|Transportation</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1509,7 +1401,6 @@
           <t>Emissions|N2O|Energy|Demand|Transportation|Light-Duty Vehicle; Emissions|N2O|Energy|Demand|Transportation|Truck</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1530,8 +1421,6 @@
           <t>Emissions|N2O|Energy|Demand|Transportation|Rail</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1552,8 +1441,6 @@
           <t>Emissions|N2O|Energy|Demand|Transportation|Domestic Shipping</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1574,8 +1461,6 @@
           <t>Emissions|N2O|Energy|Demand|Transportation|Domestic Aviation</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1596,8 +1481,6 @@
           <t>Emissions|N2O|Energy|Demand|Residential and Commercial</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1618,8 +1501,6 @@
           <t>Emissions|N2O|Energy|Demand|Residential</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1640,8 +1521,6 @@
           <t>Emissions|N2O|Energy|Demand|Commercial</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1662,8 +1541,6 @@
           <t>Emissions|N2O|Energy|Demand|AFOFI</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1681,11 +1558,9 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Carbon Capture</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+          <t>Carbon Capture|Geological Storage</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1706,8 +1581,6 @@
           <t>Carbon Capture|Energy|Supply</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1728,8 +1601,6 @@
           <t>Carbon Capture|Energy|Supply|Electricity</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1745,9 +1616,6 @@
           <t>Carbon Sequestration|CCS|Energy|Supply|Heat</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1768,8 +1636,6 @@
           <t>Carbon Capture|Energy|Supply|Hydrogen</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1790,12 +1656,6 @@
           <t>Carbon Capture|Energy|Supply|Liquids</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Carbon Capture|Energy|Supply|Fossil</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1813,13 +1673,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Carbon Capture|Energy|Demand</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Carbon Capture|Utilization</t>
+          <t>Carbon Capture|Geological Storage|Energy|Demand</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Carbon Capture|Industrial Processes|Non-Metallic Minerals</t>
         </is>
       </c>
     </row>
@@ -1839,11 +1698,9 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Carbon Capture|Energy|Demand|Industry|Chemicals</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+          <t>Carbon Capture|Geological Storage|Energy|Demand|Industry|Chemicals</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1861,11 +1718,9 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Carbon Capture|Energy|Demand|Industry|Iron and Steel</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+          <t>Carbon Capture|Geological Storage|Energy|Demand|Industry|Iron and Steel</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1881,9 +1736,16 @@
           <t>Carbon Sequestration|CCS|Energy|Demand|Industry|Non-Metallic Minerals</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Carbon Capture|Geological Storage|Energy|Demand|Industry|Non-Metallic Minerals</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Carbon Capture|Industrial Processes|Non-Metallic Minerals</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1901,15 +1763,14 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Carbon Capture|Energy|Demand|Industry|Other Sector</t>
+          <t>Carbon Capture|Geological Storage|Energy|Demand|Industry|Other Sector</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Carbon Capture|Energy|Demand|Industry|Non-Ferrous Metals</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
+          <t>Carbon Capture|Geological Storage|Energy|Demand|Industry|Non-Ferrous Metals</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1930,8 +1791,6 @@
           <t>Carbon Capture|Direct Air Capture</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1952,8 +1811,6 @@
           <t>Emissions|CO2|Industrial Processes|Cement</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1969,9 +1826,6 @@
           <t>Emissions|GHGs|Non-Energy|Industrial Process|Chemicals</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1992,8 +1846,6 @@
           <t>Emissions|GHGs|Non-Energy|Industrial Process|Iron and Steel</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2014,8 +1866,6 @@
           <t>Emissions|CO2|Industrial Processes|Cement</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2036,8 +1886,6 @@
           <t>Primary Energy</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2058,8 +1906,6 @@
           <t>Primary Energy|Coal</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2080,8 +1926,6 @@
           <t>Primary Energy|Biomass</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2102,8 +1946,6 @@
           <t>Primary Energy|Oil</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2124,8 +1966,6 @@
           <t>Primary Energy|Gas</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2146,8 +1986,6 @@
           <t>Primary Energy|Nuclear</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2168,8 +2006,6 @@
           <t>Primary Energy|Hydro</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2190,8 +2026,6 @@
           <t>Primary Energy|Geothermal</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2212,8 +2046,6 @@
           <t>Primary Energy|Solar</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2234,8 +2066,6 @@
           <t>Primary Energy|Wind</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2251,9 +2081,6 @@
           <t>Primary Energy|Waste</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2274,8 +2101,6 @@
           <t>Primary Energy|Other</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2291,9 +2116,6 @@
           <t>Primary Energy|Hydrogen Import</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2309,9 +2131,6 @@
           <t>Primary Energy|Coal|Electricity</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2332,8 +2151,6 @@
           <t>Primary Energy|Biomass|Electricity</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2349,9 +2166,6 @@
           <t>Primary Energy|Oil|Electricity</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2367,9 +2181,6 @@
           <t>Primary Energy|Gas|Electricity</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2385,9 +2196,6 @@
           <t>Primary Energy|Nuclear|Electricity</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2403,9 +2211,6 @@
           <t>Primary Energy|Hydro|Electricity</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2421,9 +2226,6 @@
           <t>Primary Energy|Geothermal|Electricity</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2439,9 +2241,6 @@
           <t>Primary Energy|Solar|Electricity</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2457,9 +2256,6 @@
           <t>Primary Energy|Wind|Electricity</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2475,9 +2271,6 @@
           <t>Primary Energy|Waste|Electricity</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2493,9 +2286,6 @@
           <t>Primary Energy|Other|Electricity</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2511,9 +2301,6 @@
           <t>Primary Energy|Hydrogen|Electricity</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2529,9 +2316,6 @@
           <t>Primary Energy|Coal|Heat</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2547,9 +2331,6 @@
           <t>Primary Energy|Biomass|Heat</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2565,9 +2346,6 @@
           <t>Primary Energy|Oil|Heat</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2583,9 +2361,6 @@
           <t>Primary Energy|Gas|Heat</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2601,9 +2376,6 @@
           <t>Primary Energy|Nuclear|Heat</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2619,9 +2391,6 @@
           <t>Primary Energy|Hydro|Heat</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2637,9 +2406,6 @@
           <t>Primary Energy|Geothermal|Heat</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2655,9 +2421,6 @@
           <t>Primary Energy|Solar|Heat</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2673,9 +2436,6 @@
           <t>Primary Energy|Wind|Heat</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2691,9 +2451,6 @@
           <t>Primary Energy|Waste|Heat</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2709,9 +2466,6 @@
           <t>Primary Energy|Other|Heat</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2727,9 +2481,6 @@
           <t>Primary Energy|Hydrogen|Heat</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2750,8 +2501,6 @@
           <t>Primary Energy|Coal|Hydrogen</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2772,8 +2521,6 @@
           <t>Primary Energy|Biomass|Hydrogen</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2794,8 +2541,6 @@
           <t>Primary Energy|Gas|Hydrogen</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2816,8 +2561,6 @@
           <t>Primary Energy|Electricity|Hydrogen</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2833,9 +2576,6 @@
           <t>Primary Energy|Hydrogen Import|Hydrogen</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2856,8 +2596,6 @@
           <t>Secondary Energy|Electricity</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2878,8 +2616,6 @@
           <t>Secondary Energy|Electricity|Biomass|w/ CCS</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2900,8 +2636,6 @@
           <t>Secondary Energy|Electricity|Biomass|w/o CCS</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2922,8 +2656,6 @@
           <t>Secondary Energy|Electricity|Coal|w/ CCS</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2944,8 +2676,6 @@
           <t>Secondary Energy|Electricity|Coal|w/o CCS</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2966,8 +2696,6 @@
           <t>Secondary Energy|Electricity|Gas|w/ CCS</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2988,8 +2716,6 @@
           <t>Secondary Energy|Electricity|Gas|w/o CCS</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3010,8 +2736,6 @@
           <t>Secondary Energy|Electricity|Hydro</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3032,8 +2756,6 @@
           <t>Secondary Energy|Electricity|Nuclear</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3054,8 +2776,6 @@
           <t>Secondary Energy|Electricity|Oil|w/ CCS</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3076,8 +2796,6 @@
           <t>Secondary Energy|Electricity|Oil|w/o CCS</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3098,8 +2816,6 @@
           <t>Secondary Energy|Electricity|Solar|CSP</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3120,8 +2836,6 @@
           <t>Secondary Energy|Electricity|Solar|PV</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3142,8 +2856,6 @@
           <t>Secondary Energy|Electricity|Wind|Offshore</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3164,8 +2876,6 @@
           <t>Secondary Energy|Electricity|Wind|Onshore</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3181,9 +2891,6 @@
           <t>Secondary Energy|Electricity|Hydrogen</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3204,8 +2911,6 @@
           <t>Secondary Energy|Electricity|Other</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3226,8 +2931,6 @@
           <t>Secondary Energy|Heat</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3243,9 +2946,6 @@
           <t>Secondary Energy|Heat|Biomass|w/ CCS</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3261,9 +2961,6 @@
           <t>Secondary Energy|Heat|Biomass|w/o CCS</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3279,9 +2976,6 @@
           <t>Secondary Energy|Heat|Coal|w/ CCS</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3297,9 +2991,6 @@
           <t>Secondary Energy|Heat|Coal|w/o CCS</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3315,9 +3006,6 @@
           <t>Secondary Energy|Heat|Gas|w/ CCS</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3333,9 +3021,6 @@
           <t>Secondary Energy|Heat|Gas|w/o CCS</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3351,9 +3036,6 @@
           <t>Secondary Energy|Heat|Oil|w/ CCS</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3369,9 +3051,6 @@
           <t>Secondary Energy|Heat|Oil|w/o CCS</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3387,9 +3066,6 @@
           <t>Secondary Energy|Heat|Hydrogen</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3410,8 +3086,6 @@
           <t>Secondary Energy|Heat|Other</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3437,7 +3111,6 @@
           <t>Secondary Energy|Hydrogen|Other; Secondary Energy|Hydrogen|Import</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3463,7 +3136,6 @@
           <t>Secondary Energy|Hydrogen|Other</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3484,8 +3156,6 @@
           <t>Secondary Energy|Hydrogen|Coal|w/ CCS</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3506,7 +3176,6 @@
           <t>Secondary Energy|Hydrogen|Coal</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>Secondary Energy|Hydrogen|Coal|w/ CCS</t>
@@ -3532,8 +3201,6 @@
           <t>Secondary Energy|Hydrogen|Biomass</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3554,8 +3221,6 @@
           <t>Secondary Energy|Hydrogen|Gas|w/ CCS</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3576,7 +3241,6 @@
           <t>Secondary Energy|Hydrogen|Gas</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>Secondary Energy|Hydrogen|Gas|w/ CCS</t>
@@ -3602,8 +3266,6 @@
           <t>Secondary Energy|Hydrogen|Electricity</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3619,9 +3281,6 @@
           <t>Secondary Energy|Hydrogen|Import</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3642,8 +3301,6 @@
           <t>Final Energy</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3664,8 +3321,6 @@
           <t>Final Energy|Solids|Coal</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3691,7 +3346,6 @@
           <t>Final Energy|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3712,8 +3366,6 @@
           <t>Final Energy|Liquids</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3734,8 +3386,6 @@
           <t>Final Energy|Gases</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3756,8 +3406,6 @@
           <t>Final Energy|Electricity</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3778,8 +3426,6 @@
           <t>Final Energy|Heat</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3795,9 +3441,6 @@
           <t>Final Energy|Solar</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3813,9 +3456,6 @@
           <t>Final Energy|Solar|PV</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3831,9 +3471,6 @@
           <t>Final Energy|Solar|Solarthermal</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3854,8 +3491,6 @@
           <t>Final Energy|Hydrogen</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3876,8 +3511,6 @@
           <t>Final Energy|Industry</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3903,7 +3536,6 @@
           <t>Final Energy|Non-Energy Use|Solids|Coal</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3924,8 +3556,6 @@
           <t>Final Energy|Industry|Solids|Coal</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3946,8 +3576,6 @@
           <t>Final Energy|Non-Energy Use|Solids|Coal</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3973,7 +3601,6 @@
           <t>Final Energy|Industry|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3989,9 +3616,6 @@
           <t>Final Energy|Industry|Biomass|Fuel</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4007,9 +3631,6 @@
           <t>Final Energy|Industry|Biomass|Feedstock</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4030,8 +3651,6 @@
           <t>Final Energy|Industry|Solids|Biomass</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4052,8 +3671,6 @@
           <t>Final Energy|Industry|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4079,7 +3696,6 @@
           <t>Final Energy|Non-Energy Use|Liquids</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4100,8 +3716,6 @@
           <t>Final Energy|Industry|Liquids</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4122,8 +3736,6 @@
           <t>Final Energy|Non-Energy Use|Liquids</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4144,8 +3756,6 @@
           <t>Final Energy|Industry|Gases</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4166,8 +3776,6 @@
           <t>Final Energy|Industry|Gases</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4188,8 +3796,6 @@
           <t>Final Energy|Non-Energy Use|Gases</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4210,8 +3816,6 @@
           <t>Final Energy|Industry|Electricity</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4232,8 +3836,6 @@
           <t>Final Energy|Industry|Heat</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4249,9 +3851,6 @@
           <t>Final Energy|Industry|Solar</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4267,9 +3866,6 @@
           <t>Final Energy|Industry|Solar|PV</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4285,9 +3881,6 @@
           <t>Final Energy|Industry|Solar|Solarthermal</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4308,8 +3901,6 @@
           <t>Final Energy|Industry|Hydrogen</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -4325,9 +3916,6 @@
           <t>Final Energy|Industry|Hydrogen|Fuel</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -4343,9 +3931,6 @@
           <t>Final Energy|Industry|Hydrogen|Feedstock</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4361,9 +3946,6 @@
           <t>Final Energy|Industry|Waste</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4384,8 +3966,6 @@
           <t>Final Energy|Industry|Chemicals</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4406,8 +3986,6 @@
           <t>Final Energy|Industry|Chemicals|Solids|Coal</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -4423,9 +4001,6 @@
           <t>Final Energy|Industry|Chemicals|Coal|Fuel</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -4441,9 +4016,6 @@
           <t>Final Energy|Industry|Chemicals|Coal|Feedstock</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -4469,7 +4041,6 @@
           <t>Final Energy|Industry|Chemicals|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -4485,9 +4056,6 @@
           <t>Final Energy|Industry|Chemicals|Biomass|Fuel</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -4503,9 +4071,6 @@
           <t>Final Energy|Industry|Chemicals|Biomass|Feedstock</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4526,8 +4091,6 @@
           <t>Final Energy|Industry|Chemicals|Solids|Biomass</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4548,8 +4111,6 @@
           <t>Final Energy|Industry|Chemicals|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4570,8 +4131,6 @@
           <t>Final Energy|Industry|Chemicals|Liquids</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -4587,9 +4146,6 @@
           <t>Final Energy|Industry|Chemicals|Oil|Fuel</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
-      <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -4605,9 +4161,6 @@
           <t>Final Energy|Industry|Chemicals|Oil|Feedstock</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -4628,8 +4181,6 @@
           <t>Final Energy|Industry|Chemicals|Gases</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -4645,9 +4196,6 @@
           <t>Final Energy|Industry|Chemicals|Gas|Fuel</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
-      <c r="E202" t="inlineStr"/>
-      <c r="F202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -4663,9 +4211,6 @@
           <t>Final Energy|Industry|Chemicals|Gas|Feedstock</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -4686,8 +4231,6 @@
           <t>Final Energy|Industry|Chemicals|Electricity</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -4708,8 +4251,6 @@
           <t>Final Energy|Industry|Chemicals|Heat</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr"/>
-      <c r="F205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -4725,9 +4266,6 @@
           <t>Final Energy|Industry|Chemicals|Solar</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -4743,9 +4281,6 @@
           <t>Final Energy|Industry|Chemicals|Solar|PV</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -4761,9 +4296,6 @@
           <t>Final Energy|Industry|Chemicals|Solar|Solarthermal</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -4784,8 +4316,6 @@
           <t>Final Energy|Industry|Chemicals|Hydrogen</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr"/>
-      <c r="F209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -4801,9 +4331,6 @@
           <t>Final Energy|Industry|Chemicals|Hydrogen|Fuel</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -4819,9 +4346,6 @@
           <t>Final Energy|Industry|Chemicals|Hydrogen|Feedstock</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr"/>
-      <c r="F211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -4837,9 +4361,6 @@
           <t>Final Energy|Industry|Chemicals|Waste</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -4860,8 +4381,6 @@
           <t>Final Energy|Industry|Iron and Steel</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr"/>
-      <c r="F213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -4882,8 +4401,6 @@
           <t>Final Energy|Industry|Iron and Steel|Solids|Coal</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr"/>
-      <c r="F214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -4904,8 +4421,6 @@
           <t>Final Energy|Industry|Iron and Steel|Coal|Fuel</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr"/>
-      <c r="F215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -4926,8 +4441,6 @@
           <t>Final Energy|Industry|Iron and Steel|Coal|Feedstock</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr"/>
-      <c r="F216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -4953,7 +4466,6 @@
           <t>Final Energy|Industry|Iron and Steel|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -4969,9 +4481,6 @@
           <t>Final Energy|Industry|Iron and Steel|Biomass|Fuel</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
-      <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -4987,9 +4496,6 @@
           <t>Final Energy|Industry|Iron and Steel|Biomass|Feedstock</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -5010,8 +4516,6 @@
           <t>Final Energy|Industry|Iron and Steel|Solids|Biomass</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -5032,8 +4536,6 @@
           <t>Final Energy|Industry|Iron and Steel|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -5054,8 +4556,6 @@
           <t>Final Energy|Industry|Iron and Steel|Liquids</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -5071,9 +4571,6 @@
           <t>Final Energy|Industry|Iron and Steel|Oil|Fuel</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
-      <c r="E223" t="inlineStr"/>
-      <c r="F223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -5089,9 +4586,6 @@
           <t>Final Energy|Industry|Iron and Steel|Oil|Feedstock</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
-      <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -5112,8 +4606,6 @@
           <t>Final Energy|Industry|Iron and Steel|Gases</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr"/>
-      <c r="F225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -5129,9 +4621,6 @@
           <t>Final Energy|Industry|Iron and Steel|Gas|Fuel</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
-      <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -5147,9 +4636,6 @@
           <t>Final Energy|Industry|Iron and Steel|Gas|Feedstock</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
-      <c r="E227" t="inlineStr"/>
-      <c r="F227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -5170,8 +4656,6 @@
           <t>Final Energy|Industry|Iron and Steel|Electricity</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr"/>
-      <c r="F228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -5187,9 +4671,6 @@
           <t>Final Energy|Industry|Iron and Steel|Heat</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
-      <c r="E229" t="inlineStr"/>
-      <c r="F229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -5205,9 +4686,6 @@
           <t>Final Energy|Industry|Iron and Steel|Solar</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
-      <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -5223,9 +4701,6 @@
           <t>Final Energy|Industry|Iron and Steel|Solar|PV</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr"/>
-      <c r="F231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -5241,9 +4716,6 @@
           <t>Final Energy|Industry|Iron and Steel|Solar|Solarthermal</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
-      <c r="E232" t="inlineStr"/>
-      <c r="F232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -5264,8 +4736,6 @@
           <t>Final Energy|Industry|Iron and Steel|Hydrogen</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr"/>
-      <c r="F233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -5281,9 +4751,6 @@
           <t>Final Energy|Industry|Iron and Steel|Hydrogen|Fuel</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr"/>
-      <c r="F234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -5299,9 +4766,6 @@
           <t>Final Energy|Industry|Iron and Steel|Hydrogen|Feedstock</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -5317,9 +4781,6 @@
           <t>Final Energy|Industry|Iron and Steel|Waste</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
-      <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -5340,8 +4801,6 @@
           <t>Final Energy|Industry|Non-Metallic Minerals</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr"/>
-      <c r="F237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -5362,8 +4821,6 @@
           <t>Final Energy|Industry|Non-Metallic Minerals|Cement|Solids|Coal</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -5379,9 +4836,6 @@
           <t>Final Energy|Industry|Non-Metallic Minerals|Coal|Fuel</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
-      <c r="E239" t="inlineStr"/>
-      <c r="F239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -5397,9 +4851,6 @@
           <t>Final Energy|Industry|Non-Metallic Minerals|Coal|Feedstock</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
-      <c r="E240" t="inlineStr"/>
-      <c r="F240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -5425,7 +4876,6 @@
           <t>Final Energy|Industry|Non-Metallic Minerals|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -5441,9 +4891,6 @@
           <t>Final Energy|Industry|Non-Metallic Minerals|Biomass|Fuel</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
-      <c r="E242" t="inlineStr"/>
-      <c r="F242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -5459,9 +4906,6 @@
           <t>Final Energy|Industry|Non-Metallic Minerals|Biomass|Feedstock</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
-      <c r="E243" t="inlineStr"/>
-      <c r="F243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -5482,8 +4926,6 @@
           <t>Final Energy|Industry|Non-Metallic Minerals|Cement|Solids|Biomass</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -5504,8 +4946,6 @@
           <t>Final Energy|Industry|Non-Metallic Minerals|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr"/>
-      <c r="F245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -5526,8 +4966,6 @@
           <t>Final Energy|Industry|Non-Metallic Minerals|Cement|Liquids</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr"/>
-      <c r="F246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -5543,9 +4981,6 @@
           <t>Final Energy|Industry|Non-Metallic Minerals|Oil|Fuel</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
-      <c r="E247" t="inlineStr"/>
-      <c r="F247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -5561,9 +4996,6 @@
           <t>Final Energy|Industry|Non-Metallic Minerals|Oil|Feedstock</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
-      <c r="E248" t="inlineStr"/>
-      <c r="F248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -5584,8 +5016,6 @@
           <t>Final Energy|Industry|Non-Metallic Minerals|Cement|Gases</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr"/>
-      <c r="F249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -5601,9 +5031,6 @@
           <t>Final Energy|Industry|Non-Metallic Minerals|Gas|Fuel</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr"/>
-      <c r="F250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -5619,9 +5046,6 @@
           <t>Final Energy|Industry|Non-Metallic Minerals|Gas|Feedstock</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
-      <c r="E251" t="inlineStr"/>
-      <c r="F251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -5642,8 +5066,6 @@
           <t>Final Energy|Industry|Non-Metallic Minerals|Cement|Electricity</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr"/>
-      <c r="F252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -5659,9 +5081,6 @@
           <t>Final Energy|Industry|Non-Metallic Minerals|Heat</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
-      <c r="E253" t="inlineStr"/>
-      <c r="F253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -5677,9 +5096,6 @@
           <t>Final Energy|Industry|Non-Metallic Minerals|Solar</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
-      <c r="E254" t="inlineStr"/>
-      <c r="F254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -5695,9 +5111,6 @@
           <t>Final Energy|Industry|Non-Metallic Minerals|Solar|PV</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
-      <c r="E255" t="inlineStr"/>
-      <c r="F255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -5713,9 +5126,6 @@
           <t>Final Energy|Industry|Non-Metallic Minerals|Solar|Solarthermal</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
-      <c r="E256" t="inlineStr"/>
-      <c r="F256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -5736,8 +5146,6 @@
           <t>Final Energy|Industry|Non-Metallic Minerals|Cement|Hydrogen</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr"/>
-      <c r="F257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -5753,9 +5161,6 @@
           <t>Final Energy|Industry|Non-Metallic Minerals|Hydrogen|Fuel</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
-      <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -5771,9 +5176,6 @@
           <t>Final Energy|Industry|Non-Metallic Minerals|Hydrogen|Feedstock</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
-      <c r="E259" t="inlineStr"/>
-      <c r="F259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -5789,9 +5191,6 @@
           <t>Final Energy|Industry|Non-Metallic Minerals|Waste</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
-      <c r="E260" t="inlineStr"/>
-      <c r="F260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -5812,8 +5211,6 @@
           <t>Final Energy|Industry|Other Sector</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -5834,8 +5231,6 @@
           <t>Final Energy|Industry|Other Sector|Solids|Coal</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr"/>
-      <c r="F262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -5851,9 +5246,6 @@
           <t>Final Energy|Industry|Other Sector|Coal|Fuel</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
-      <c r="E263" t="inlineStr"/>
-      <c r="F263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -5869,9 +5261,6 @@
           <t>Final Energy|Industry|Other Sector|Coal|Feedstock</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
-      <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -5897,7 +5286,6 @@
           <t>Final Energy|Industry|Other Sector|biomass|Liquids</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -5913,9 +5301,6 @@
           <t>Final Energy|Industry|Other Sector|Biomass|Fuel</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
-      <c r="E266" t="inlineStr"/>
-      <c r="F266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -5931,9 +5316,6 @@
           <t>Final Energy|Industry|Other Sector|Biomass|Feedstock</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
-      <c r="E267" t="inlineStr"/>
-      <c r="F267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -5954,8 +5336,6 @@
           <t>Final Energy|Industry|Other Sector|Solids|Biomass</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr"/>
-      <c r="F268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -5976,8 +5356,6 @@
           <t>Final Energy|Industry|Other Sector|biomass|Liquids</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr"/>
-      <c r="F269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -5998,8 +5376,6 @@
           <t>Final Energy|Industry|Other Sector|Liquids</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr"/>
-      <c r="F270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -6015,9 +5391,6 @@
           <t>Final Energy|Industry|Other Sector|Oil|Feedstock</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
-      <c r="E271" t="inlineStr"/>
-      <c r="F271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -6038,8 +5411,6 @@
           <t>Final Energy|Industry|Other Sector|Gases</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr"/>
-      <c r="F272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -6055,9 +5426,6 @@
           <t>Final Energy|Industry|Other Sector|Gas|Fuel</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
-      <c r="E273" t="inlineStr"/>
-      <c r="F273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -6073,9 +5441,6 @@
           <t>Final Energy|Industry|Other Sector|Gas|Feedstock</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
-      <c r="E274" t="inlineStr"/>
-      <c r="F274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -6096,8 +5461,6 @@
           <t>Final Energy|Industry|Other Sector|Electricity</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr"/>
-      <c r="F275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -6118,8 +5481,6 @@
           <t>Final Energy|Industry|Other Sector|Heat</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr"/>
-      <c r="F276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -6135,9 +5496,6 @@
           <t>Final Energy|Industry|Other Sector|Solar</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
-      <c r="E277" t="inlineStr"/>
-      <c r="F277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -6153,9 +5511,6 @@
           <t>Final Energy|Industry|Other Sector|Solar|PV</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
-      <c r="E278" t="inlineStr"/>
-      <c r="F278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -6171,9 +5526,6 @@
           <t>Final Energy|Industry|Other Sector|Solar|Solarthermal</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
-      <c r="E279" t="inlineStr"/>
-      <c r="F279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -6194,8 +5546,6 @@
           <t>Final Energy|Industry|Other Sector|Hydrogen</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr"/>
-      <c r="F280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -6211,9 +5561,6 @@
           <t>Final Energy|Industry|Other Sector|Hydrogen|Fuel</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
-      <c r="E281" t="inlineStr"/>
-      <c r="F281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -6229,9 +5576,6 @@
           <t>Final Energy|Industry|Other Sector|Hydrogen|Feedstock</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
-      <c r="E282" t="inlineStr"/>
-      <c r="F282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -6247,9 +5591,6 @@
           <t>Final Energy|Industry|Other Sector|Waste</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
-      <c r="E283" t="inlineStr"/>
-      <c r="F283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -6270,8 +5611,6 @@
           <t>Final Energy|Transportation</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr"/>
-      <c r="F284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -6292,8 +5631,6 @@
           <t>Final Energy|Transportation|Solids|Coal</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr"/>
-      <c r="F285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -6314,8 +5651,6 @@
           <t>Final Energy|Transportation|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr"/>
-      <c r="F286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -6331,9 +5666,6 @@
           <t>Final Energy|Transportation|Biomass|Solids</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
-      <c r="E287" t="inlineStr"/>
-      <c r="F287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -6354,8 +5686,6 @@
           <t>Final Energy|Transportation|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr"/>
-      <c r="F288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -6376,8 +5706,6 @@
           <t>Final Energy|Transportation|Liquids</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr"/>
-      <c r="F289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -6398,8 +5726,6 @@
           <t>Final Energy|Transportation|Gases</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr"/>
-      <c r="F290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -6420,8 +5746,6 @@
           <t>Final Energy|Transportation|Electricity</t>
         </is>
       </c>
-      <c r="E291" t="inlineStr"/>
-      <c r="F291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -6437,9 +5761,6 @@
           <t>Final Energy|Transportation|Heat</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
-      <c r="E292" t="inlineStr"/>
-      <c r="F292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -6455,9 +5776,6 @@
           <t>Final Energy|Transportation|Solar</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
-      <c r="E293" t="inlineStr"/>
-      <c r="F293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -6478,8 +5796,6 @@
           <t>Final Energy|Transportation|Hydrogen</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr"/>
-      <c r="F294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -6505,7 +5821,6 @@
           <t>Final Energy|Transportation|Light-Duty Vehicle; Final Energy|Transportation|Truck</t>
         </is>
       </c>
-      <c r="F295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -6521,9 +5836,6 @@
           <t>Final Energy|Transportation|Road|Coal</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
-      <c r="E296" t="inlineStr"/>
-      <c r="F296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -6544,8 +5856,6 @@
           <t>Final Energy|Transportation|Road|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="E297" t="inlineStr"/>
-      <c r="F297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -6561,9 +5871,6 @@
           <t>Final Energy|Transportation|Road|Biomass|Solids</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
-      <c r="E298" t="inlineStr"/>
-      <c r="F298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -6584,8 +5891,6 @@
           <t>Final Energy|Transportation|Road|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr"/>
-      <c r="F299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -6611,7 +5916,6 @@
           <t>Final Energy|Transportation|Light-Duty Vehicle|Liquids; Final Energy|Transportation|Truck|Liquids</t>
         </is>
       </c>
-      <c r="F300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -6637,7 +5941,6 @@
           <t>Final Energy|Transportation|Light-Duty Vehicle|Gases; Final Energy|Transportation|Truck|Gases</t>
         </is>
       </c>
-      <c r="F301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -6663,7 +5966,6 @@
           <t>Final Energy|Transportation|Light-Duty Vehicle|Electricity; Final Energy|Transportation|Truck|Electricity</t>
         </is>
       </c>
-      <c r="F302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -6679,9 +5981,6 @@
           <t>Final Energy|Transportation|Road|Heat</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
-      <c r="E303" t="inlineStr"/>
-      <c r="F303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -6697,9 +5996,6 @@
           <t>Final Energy|Transportation|Road|Solar</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
-      <c r="E304" t="inlineStr"/>
-      <c r="F304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -6725,7 +6021,6 @@
           <t>Final Energy|Transportation|Light-Duty Vehicle|Hydrogen; Final Energy|Transportation|Truck|Hydrogen</t>
         </is>
       </c>
-      <c r="F305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -6746,8 +6041,6 @@
           <t>Final Energy|Transportation|Rail</t>
         </is>
       </c>
-      <c r="E306" t="inlineStr"/>
-      <c r="F306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -6763,9 +6056,6 @@
           <t>Final Energy|Transportation|Rail|Coal</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
-      <c r="E307" t="inlineStr"/>
-      <c r="F307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -6786,8 +6076,6 @@
           <t>Final Energy|Transportation|Rail|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr"/>
-      <c r="F308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -6803,9 +6091,6 @@
           <t>Final Energy|Transportation|Rail|Biomass|Solids</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
-      <c r="E309" t="inlineStr"/>
-      <c r="F309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -6826,8 +6111,6 @@
           <t>Final Energy|Transportation|Rail|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr"/>
-      <c r="F310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -6843,9 +6126,6 @@
           <t>Final Energy|Transportation|Rail|Oil</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
-      <c r="E311" t="inlineStr"/>
-      <c r="F311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -6861,9 +6141,6 @@
           <t>Final Energy|Transportation|Rail|Gas</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
-      <c r="E312" t="inlineStr"/>
-      <c r="F312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -6884,8 +6161,6 @@
           <t>Final Energy|Transportation|Rail|Electricity</t>
         </is>
       </c>
-      <c r="E313" t="inlineStr"/>
-      <c r="F313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -6901,9 +6176,6 @@
           <t>Final Energy|Transportation|Rail|Heat</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
-      <c r="E314" t="inlineStr"/>
-      <c r="F314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -6919,9 +6191,6 @@
           <t>Final Energy|Transportation|Rail|Solar</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
-      <c r="E315" t="inlineStr"/>
-      <c r="F315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -6942,8 +6211,6 @@
           <t>Final Energy|Transportation|Rail|Hydrogen</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr"/>
-      <c r="F316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -6964,8 +6231,6 @@
           <t>Final Energy|Transportation|Domestic Shipping</t>
         </is>
       </c>
-      <c r="E317" t="inlineStr"/>
-      <c r="F317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -6981,9 +6246,6 @@
           <t>Final Energy|Transportation|Ship|Coal</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
-      <c r="E318" t="inlineStr"/>
-      <c r="F318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -7004,8 +6266,6 @@
           <t>Final Energy|Transportation|Ship|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="E319" t="inlineStr"/>
-      <c r="F319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -7021,9 +6281,6 @@
           <t>Final Energy|Transportation|Ship|Biomass|Solids</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
-      <c r="E320" t="inlineStr"/>
-      <c r="F320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -7044,8 +6301,6 @@
           <t>Final Energy|Transportation|Ship|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="E321" t="inlineStr"/>
-      <c r="F321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -7066,8 +6321,6 @@
           <t>Final Energy|Transportation|Domestic Shipping|Liquids</t>
         </is>
       </c>
-      <c r="E322" t="inlineStr"/>
-      <c r="F322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -7083,9 +6336,6 @@
           <t>Final Energy|Transportation|Ship|Gas</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
-      <c r="E323" t="inlineStr"/>
-      <c r="F323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -7106,8 +6356,6 @@
           <t>Final Energy|Transportation|Domestic Shipping|Electricity</t>
         </is>
       </c>
-      <c r="E324" t="inlineStr"/>
-      <c r="F324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -7123,9 +6371,6 @@
           <t>Final Energy|Transportation|Ship|Heat</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
-      <c r="E325" t="inlineStr"/>
-      <c r="F325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -7141,9 +6386,6 @@
           <t>Final Energy|Transportation|Ship|Solar</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
-      <c r="E326" t="inlineStr"/>
-      <c r="F326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -7164,8 +6406,6 @@
           <t>Final Energy|Transportation|Domestic Shipping|Hydrogen</t>
         </is>
       </c>
-      <c r="E327" t="inlineStr"/>
-      <c r="F327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -7186,8 +6426,6 @@
           <t>Final Energy|Transportation|Domestic Aviation</t>
         </is>
       </c>
-      <c r="E328" t="inlineStr"/>
-      <c r="F328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -7203,9 +6441,6 @@
           <t>Final Energy|Transportation|Air|Coal</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
-      <c r="E329" t="inlineStr"/>
-      <c r="F329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -7226,8 +6461,6 @@
           <t>Final Energy|Transportation|Air|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="E330" t="inlineStr"/>
-      <c r="F330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -7243,9 +6476,6 @@
           <t>Final Energy|Transportation|Air|Biomass|Solids</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr"/>
-      <c r="F331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -7266,8 +6496,6 @@
           <t>Final Energy|Transportation|Air|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="E332" t="inlineStr"/>
-      <c r="F332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -7288,8 +6516,6 @@
           <t>Final Energy|Transportation|Domestic Aviation|Liquids</t>
         </is>
       </c>
-      <c r="E333" t="inlineStr"/>
-      <c r="F333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -7305,9 +6531,6 @@
           <t>Final Energy|Transportation|Air|Gas</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr"/>
-      <c r="F334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -7328,8 +6551,6 @@
           <t>Final Energy|Transportation|Domestic Aviation|Electricity</t>
         </is>
       </c>
-      <c r="E335" t="inlineStr"/>
-      <c r="F335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -7345,9 +6566,6 @@
           <t>Final Energy|Transportation|Air|Heat</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
-      <c r="E336" t="inlineStr"/>
-      <c r="F336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -7363,9 +6581,6 @@
           <t>Final Energy|Transportation|Air|Solar</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
-      <c r="E337" t="inlineStr"/>
-      <c r="F337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -7386,8 +6601,6 @@
           <t>Final Energy|Transportation|Domestic Aviation|Hydrogen</t>
         </is>
       </c>
-      <c r="E338" t="inlineStr"/>
-      <c r="F338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -7408,8 +6621,6 @@
           <t>Final Energy|Residential and Commercial</t>
         </is>
       </c>
-      <c r="E339" t="inlineStr"/>
-      <c r="F339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -7430,8 +6641,6 @@
           <t>Final Energy|Residential and Commercial|Solids|Coal</t>
         </is>
       </c>
-      <c r="E340" t="inlineStr"/>
-      <c r="F340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -7457,7 +6666,6 @@
           <t>Final Energy|Building|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="F341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -7478,8 +6686,6 @@
           <t>Final Energy|Residential and Commercial|Solids|Biomass</t>
         </is>
       </c>
-      <c r="E342" t="inlineStr"/>
-      <c r="F342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -7500,8 +6706,6 @@
           <t>Final Energy|Building|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="E343" t="inlineStr"/>
-      <c r="F343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -7522,8 +6726,6 @@
           <t>Final Energy|Residential and Commercial|Liquids</t>
         </is>
       </c>
-      <c r="E344" t="inlineStr"/>
-      <c r="F344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -7544,8 +6746,6 @@
           <t>Final Energy|Residential and Commercial|Gases</t>
         </is>
       </c>
-      <c r="E345" t="inlineStr"/>
-      <c r="F345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -7566,8 +6766,6 @@
           <t>Final Energy|Residential and Commercial|Electricity</t>
         </is>
       </c>
-      <c r="E346" t="inlineStr"/>
-      <c r="F346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -7588,8 +6786,6 @@
           <t>Final Energy|Residential and Commercial|Heat</t>
         </is>
       </c>
-      <c r="E347" t="inlineStr"/>
-      <c r="F347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -7605,9 +6801,6 @@
           <t>Final Energy|Building|Solar</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
-      <c r="E348" t="inlineStr"/>
-      <c r="F348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -7628,8 +6821,6 @@
           <t>Final Energy|Residential and Commercial|Hydrogen</t>
         </is>
       </c>
-      <c r="E349" t="inlineStr"/>
-      <c r="F349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -7645,9 +6836,6 @@
           <t>Final Energy|Building|Waste</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
-      <c r="E350" t="inlineStr"/>
-      <c r="F350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -7668,8 +6856,6 @@
           <t>Final Energy|Residential</t>
         </is>
       </c>
-      <c r="E351" t="inlineStr"/>
-      <c r="F351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -7690,8 +6876,6 @@
           <t>Final Energy|Residential|Solids|Coal</t>
         </is>
       </c>
-      <c r="E352" t="inlineStr"/>
-      <c r="F352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -7717,7 +6901,6 @@
           <t>Final Energy|Building|Residential|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="F353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -7738,8 +6921,6 @@
           <t>Final Energy|Residential|Solids|Biomass</t>
         </is>
       </c>
-      <c r="E354" t="inlineStr"/>
-      <c r="F354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -7760,8 +6941,6 @@
           <t>Final Energy|Building|Residential|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="E355" t="inlineStr"/>
-      <c r="F355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -7782,8 +6961,6 @@
           <t>Final Energy|Residential|Liquids</t>
         </is>
       </c>
-      <c r="E356" t="inlineStr"/>
-      <c r="F356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -7804,8 +6981,6 @@
           <t>Final Energy|Residential|Gases</t>
         </is>
       </c>
-      <c r="E357" t="inlineStr"/>
-      <c r="F357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -7826,8 +7001,6 @@
           <t>Final Energy|Residential|Electricity</t>
         </is>
       </c>
-      <c r="E358" t="inlineStr"/>
-      <c r="F358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -7843,9 +7016,6 @@
           <t>Final Energy|Building|Residential|Heat</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
-      <c r="E359" t="inlineStr"/>
-      <c r="F359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -7861,9 +7031,6 @@
           <t>Final Energy|Building|Residential|Solar</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
-      <c r="E360" t="inlineStr"/>
-      <c r="F360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -7879,9 +7046,6 @@
           <t>Final Energy|Building|Residential|Hydrogen</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr"/>
-      <c r="E361" t="inlineStr"/>
-      <c r="F361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -7897,9 +7061,6 @@
           <t>Final Energy|Building|Residential|Waste</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
-      <c r="E362" t="inlineStr"/>
-      <c r="F362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -7920,8 +7081,6 @@
           <t>Final Energy|Commercial</t>
         </is>
       </c>
-      <c r="E363" t="inlineStr"/>
-      <c r="F363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -7937,9 +7096,6 @@
           <t>Final Energy|Building|Commercial/Public|Coal</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr"/>
-      <c r="E364" t="inlineStr"/>
-      <c r="F364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -7965,7 +7121,6 @@
           <t>Final Energy|Building|Commercial/Public|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="F365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -7986,8 +7141,6 @@
           <t>Final Energy|Commercial|Solids|Biomass</t>
         </is>
       </c>
-      <c r="E366" t="inlineStr"/>
-      <c r="F366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -8008,8 +7161,6 @@
           <t>Final Energy|Building|Commercial/Public|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="E367" t="inlineStr"/>
-      <c r="F367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -8030,8 +7181,6 @@
           <t>Final Energy|Commercial|Liquids</t>
         </is>
       </c>
-      <c r="E368" t="inlineStr"/>
-      <c r="F368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -8052,8 +7201,6 @@
           <t>Final Energy|Commercial|Gases</t>
         </is>
       </c>
-      <c r="E369" t="inlineStr"/>
-      <c r="F369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -8074,8 +7221,6 @@
           <t>Final Energy|Commercial|Electricity</t>
         </is>
       </c>
-      <c r="E370" t="inlineStr"/>
-      <c r="F370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -8091,9 +7236,6 @@
           <t>Final Energy|Building|Commercial/Public|Heat</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr"/>
-      <c r="F371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -8109,9 +7251,6 @@
           <t>Final Energy|Building|Commercial/Public|Solar</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr"/>
-      <c r="F372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -8127,9 +7266,6 @@
           <t>Final Energy|Building|Commercial/Public|Hydrogen</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
-      <c r="E373" t="inlineStr"/>
-      <c r="F373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -8145,9 +7281,6 @@
           <t>Final Energy|Building|Commercial/Public|Waste</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
-      <c r="E374" t="inlineStr"/>
-      <c r="F374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -8168,8 +7301,6 @@
           <t>Final Energy|Agriculture</t>
         </is>
       </c>
-      <c r="E375" t="inlineStr"/>
-      <c r="F375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -8190,8 +7321,6 @@
           <t>Final Energy|Agriculture|Solids|Coal</t>
         </is>
       </c>
-      <c r="E376" t="inlineStr"/>
-      <c r="F376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -8217,7 +7346,6 @@
           <t>Final Energy|AFOFI|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="F377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -8238,8 +7366,6 @@
           <t>Final Energy|Agriculture|Solids|Biomass</t>
         </is>
       </c>
-      <c r="E378" t="inlineStr"/>
-      <c r="F378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -8260,8 +7386,6 @@
           <t>Final Energy|AFOFI|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="E379" t="inlineStr"/>
-      <c r="F379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -8282,8 +7406,6 @@
           <t>Final Energy|Agriculture|Liquids</t>
         </is>
       </c>
-      <c r="E380" t="inlineStr"/>
-      <c r="F380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -8304,8 +7426,6 @@
           <t>Final Energy|Agriculture|Gases</t>
         </is>
       </c>
-      <c r="E381" t="inlineStr"/>
-      <c r="F381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -8326,8 +7446,6 @@
           <t>Final Energy|Agriculture|Electricity</t>
         </is>
       </c>
-      <c r="E382" t="inlineStr"/>
-      <c r="F382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -8348,8 +7466,6 @@
           <t>Final Energy|Agriculture|Heat</t>
         </is>
       </c>
-      <c r="E383" t="inlineStr"/>
-      <c r="F383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -8365,9 +7481,6 @@
           <t>Final Energy|AFOFI|Solar</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
-      <c r="E384" t="inlineStr"/>
-      <c r="F384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -8388,8 +7501,6 @@
           <t>Final Energy|Agriculture|Hydrogen</t>
         </is>
       </c>
-      <c r="E385" t="inlineStr"/>
-      <c r="F385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -8405,9 +7516,6 @@
           <t>Final Energy|AFOFI|Waste</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
-      <c r="E386" t="inlineStr"/>
-      <c r="F386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -8428,8 +7536,6 @@
           <t>Final Energy|Carbon Management|Direct Air Capture</t>
         </is>
       </c>
-      <c r="E387" t="inlineStr"/>
-      <c r="F387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -8445,9 +7551,6 @@
           <t>Final Energy|Direct Air Capture|Coal</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr"/>
-      <c r="E388" t="inlineStr"/>
-      <c r="F388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -8468,8 +7571,6 @@
           <t>Final Energy|Direct Air Capture|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="E389" t="inlineStr"/>
-      <c r="F389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -8485,9 +7586,6 @@
           <t>Final Energy|Direct Air Capture|Biomass|Solids</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
-      <c r="E390" t="inlineStr"/>
-      <c r="F390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -8508,8 +7606,6 @@
           <t>Final Energy|Direct Air Capture|Biomass|Liquids</t>
         </is>
       </c>
-      <c r="E391" t="inlineStr"/>
-      <c r="F391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -8525,9 +7621,6 @@
           <t>Final Energy|Direct Air Capture|Oil</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
-      <c r="E392" t="inlineStr"/>
-      <c r="F392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -8548,8 +7641,6 @@
           <t>Final Energy|Carbon Management|Direct Air Capture|Gases</t>
         </is>
       </c>
-      <c r="E393" t="inlineStr"/>
-      <c r="F393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -8570,8 +7661,6 @@
           <t>Final Energy|Carbon Management|Direct Air Capture|Electricity</t>
         </is>
       </c>
-      <c r="E394" t="inlineStr"/>
-      <c r="F394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -8587,9 +7676,6 @@
           <t>Final Energy|Direct Air Capture|Heat</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
-      <c r="E395" t="inlineStr"/>
-      <c r="F395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -8605,9 +7691,6 @@
           <t>Final Energy|Direct Air Capture|Solar</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
-      <c r="E396" t="inlineStr"/>
-      <c r="F396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -8623,9 +7706,6 @@
           <t>Final Energy|Direct Air Capture|Hydrogen</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
-      <c r="E397" t="inlineStr"/>
-      <c r="F397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -8641,9 +7721,6 @@
           <t>Final Energy|Direct Air Capture|Waste</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr"/>
-      <c r="E398" t="inlineStr"/>
-      <c r="F398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -8664,8 +7741,6 @@
           <t>Capacity|Electricity</t>
         </is>
       </c>
-      <c r="E399" t="inlineStr"/>
-      <c r="F399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -8686,8 +7761,6 @@
           <t>Capacity|Electricity|Biomass|w/ CCS</t>
         </is>
       </c>
-      <c r="E400" t="inlineStr"/>
-      <c r="F400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -8708,8 +7781,6 @@
           <t>Capacity|Electricity|Biomass|w/o CCS</t>
         </is>
       </c>
-      <c r="E401" t="inlineStr"/>
-      <c r="F401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -8730,8 +7801,6 @@
           <t>Capacity|Electricity|Coal|w/ CCS</t>
         </is>
       </c>
-      <c r="E402" t="inlineStr"/>
-      <c r="F402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -8752,8 +7821,6 @@
           <t>Capacity|Electricity|Coal|w/o CCS</t>
         </is>
       </c>
-      <c r="E403" t="inlineStr"/>
-      <c r="F403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -8774,8 +7841,6 @@
           <t>Capacity|Electricity|Gas|w/ CCS</t>
         </is>
       </c>
-      <c r="E404" t="inlineStr"/>
-      <c r="F404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -8796,8 +7861,6 @@
           <t>Capacity|Electricity|Gas|w/o CCS</t>
         </is>
       </c>
-      <c r="E405" t="inlineStr"/>
-      <c r="F405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -8818,8 +7881,6 @@
           <t>Capacity|Electricity|Hydro</t>
         </is>
       </c>
-      <c r="E406" t="inlineStr"/>
-      <c r="F406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -8840,8 +7901,6 @@
           <t>Capacity|Electricity|Nuclear</t>
         </is>
       </c>
-      <c r="E407" t="inlineStr"/>
-      <c r="F407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -8862,8 +7921,6 @@
           <t>Capacity|Electricity|Oil|w/ CCS</t>
         </is>
       </c>
-      <c r="E408" t="inlineStr"/>
-      <c r="F408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -8884,8 +7941,6 @@
           <t>Capacity|Electricity|Oil|w/o CCS</t>
         </is>
       </c>
-      <c r="E409" t="inlineStr"/>
-      <c r="F409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -8906,8 +7961,6 @@
           <t>Capacity|Electricity|Solar|CSP</t>
         </is>
       </c>
-      <c r="E410" t="inlineStr"/>
-      <c r="F410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -8928,8 +7981,6 @@
           <t>Capacity|Electricity|Solar|PV</t>
         </is>
       </c>
-      <c r="E411" t="inlineStr"/>
-      <c r="F411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -8950,8 +8001,6 @@
           <t>Capacity|Electricity|Wind|Offshore</t>
         </is>
       </c>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -8972,8 +8021,6 @@
           <t>Capacity|Electricity|Wind|Onshore</t>
         </is>
       </c>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -8989,9 +8036,6 @@
           <t>Capacity|Electricity|Hydrogen</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -9017,7 +8061,6 @@
           <t>Capacity|Electricity|Solar|PV|Battery Storage</t>
         </is>
       </c>
-      <c r="F415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -9033,9 +8076,6 @@
           <t>Capacity|Electricity|Storage|PSH</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
-      <c r="E416" t="inlineStr"/>
-      <c r="F416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -9051,9 +8091,6 @@
           <t>Capacity|Electricity|Storage|Hydrogen</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
-      <c r="E417" t="inlineStr"/>
-      <c r="F417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -9069,9 +8106,6 @@
           <t>Capacity|Hydrogen|Domestic</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr"/>
-      <c r="E418" t="inlineStr"/>
-      <c r="F418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -9087,9 +8121,6 @@
           <t>Capacity|Hydrogen|Domestic|Coal|w/ CCS</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
-      <c r="E419" t="inlineStr"/>
-      <c r="F419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -9105,9 +8136,6 @@
           <t>Capacity|Hydrogen|Domestic|Coal|w/o CCS</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
-      <c r="E420" t="inlineStr"/>
-      <c r="F420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -9123,9 +8151,6 @@
           <t>Capacity|Hydrogen|Domestic|Biomass</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr"/>
-      <c r="E421" t="inlineStr"/>
-      <c r="F421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -9141,9 +8166,6 @@
           <t>Capacity|Hydrogen|Domestic|Gas|w/ CCS</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr"/>
-      <c r="E422" t="inlineStr"/>
-      <c r="F422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -9159,9 +8181,6 @@
           <t>Capacity|Hydrogen|Domestic|Gas|w/o CCS</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
-      <c r="E423" t="inlineStr"/>
-      <c r="F423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -9177,9 +8196,6 @@
           <t>Capacity|Hydrogen|Domestic|Electricity</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr"/>
-      <c r="E424" t="inlineStr"/>
-      <c r="F424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -9205,7 +8221,6 @@
           <t>Energy Service|Transportation|Freight|Truck</t>
         </is>
       </c>
-      <c r="F425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -9226,8 +8241,11 @@
           <t>Energy Service|Transportation|Passenger|Road|Light-Duty Vehicle|Internal Combustion</t>
         </is>
       </c>
-      <c r="E426" t="inlineStr"/>
-      <c r="F426" t="inlineStr"/>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Energy Service|Transportation|Passenger|Road|Light-Duty Vehicle|Hybrid</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -9245,11 +8263,9 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Energy Service|Transportation|Passenger|Road|Light-Duty Vehicle|Plug-in Hybrid</t>
-        </is>
-      </c>
-      <c r="E427" t="inlineStr"/>
-      <c r="F427" t="inlineStr"/>
+          <t>Energy Service|Transportation|Passenger|Road|Light-Duty Vehicle|Hybrid</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -9265,9 +8281,6 @@
           <t>Capacity|Transport|Road|LDV|PHEV</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
-      <c r="E428" t="inlineStr"/>
-      <c r="F428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -9288,8 +8301,6 @@
           <t>Energy Service|Transportation|Passenger|Road|Light-Duty Vehicle|Battery-Electric</t>
         </is>
       </c>
-      <c r="E429" t="inlineStr"/>
-      <c r="F429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -9310,8 +8321,6 @@
           <t>Energy Service|Transportation|Passenger|Road|Light-Duty Vehicle|Fuel-Cell-Electric</t>
         </is>
       </c>
-      <c r="E430" t="inlineStr"/>
-      <c r="F430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -9332,8 +8341,11 @@
           <t>Energy Service|Transportation|Freight|Truck|Internal Combustion</t>
         </is>
       </c>
-      <c r="E431" t="inlineStr"/>
-      <c r="F431" t="inlineStr"/>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Energy Service|Transportation|Freight|Truck|Hybrid</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -9351,11 +8363,9 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Energy Service|Transportation|Freight|Truck|Plug-in Hybrid</t>
-        </is>
-      </c>
-      <c r="E432" t="inlineStr"/>
-      <c r="F432" t="inlineStr"/>
+          <t>Energy Service|Transportation|Freight|Truck|Hybrid</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -9371,9 +8381,6 @@
           <t>Capacity|Transport|Road|MHDV|PHEV</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
-      <c r="E433" t="inlineStr"/>
-      <c r="F433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -9394,8 +8401,6 @@
           <t>Energy Service|Transportation|Freight|Truck|Battery-Electric</t>
         </is>
       </c>
-      <c r="E434" t="inlineStr"/>
-      <c r="F434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -9411,9 +8416,11 @@
           <t>Capacity|Transport|Road|MHDV|FCEV</t>
         </is>
       </c>
-      <c r="D435" t="inlineStr"/>
-      <c r="E435" t="inlineStr"/>
-      <c r="F435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Energy Service|Transportation|Freight|Truck|Fuel-Cell-Electric</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -9434,8 +8441,6 @@
           <t>Capacity Additions|Electricity</t>
         </is>
       </c>
-      <c r="E436" t="inlineStr"/>
-      <c r="F436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -9456,8 +8461,6 @@
           <t>Capacity Additions|Electricity|Biomass|w/ CCS</t>
         </is>
       </c>
-      <c r="E437" t="inlineStr"/>
-      <c r="F437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -9478,8 +8481,6 @@
           <t>Capacity Additions|Electricity|Biomass|w/o CCS</t>
         </is>
       </c>
-      <c r="E438" t="inlineStr"/>
-      <c r="F438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -9500,8 +8501,6 @@
           <t>Capacity Additions|Electricity|Coal|w/ CCS</t>
         </is>
       </c>
-      <c r="E439" t="inlineStr"/>
-      <c r="F439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -9522,8 +8521,6 @@
           <t>Capacity Additions|Electricity|Coal|w/o CCS</t>
         </is>
       </c>
-      <c r="E440" t="inlineStr"/>
-      <c r="F440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -9544,8 +8541,6 @@
           <t>Capacity Additions|Electricity|Gas|w/ CCS</t>
         </is>
       </c>
-      <c r="E441" t="inlineStr"/>
-      <c r="F441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -9566,8 +8561,6 @@
           <t>Capacity Additions|Electricity|Gas|w/o CCS</t>
         </is>
       </c>
-      <c r="E442" t="inlineStr"/>
-      <c r="F442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -9588,8 +8581,6 @@
           <t>Capacity Additions|Electricity|Hydro</t>
         </is>
       </c>
-      <c r="E443" t="inlineStr"/>
-      <c r="F443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -9610,8 +8601,6 @@
           <t>Capacity Additions|Electricity|Nuclear</t>
         </is>
       </c>
-      <c r="E444" t="inlineStr"/>
-      <c r="F444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -9632,8 +8621,6 @@
           <t>Capacity Additions|Electricity|Oil|w/ CCS</t>
         </is>
       </c>
-      <c r="E445" t="inlineStr"/>
-      <c r="F445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -9654,8 +8641,6 @@
           <t>Capacity Additions|Electricity|Oil|w/o CCS</t>
         </is>
       </c>
-      <c r="E446" t="inlineStr"/>
-      <c r="F446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -9676,8 +8661,6 @@
           <t>Capacity Additions|Electricity|Solar|CSP</t>
         </is>
       </c>
-      <c r="E447" t="inlineStr"/>
-      <c r="F447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -9698,8 +8681,6 @@
           <t>Capacity Additions|Electricity|Solar|PV</t>
         </is>
       </c>
-      <c r="E448" t="inlineStr"/>
-      <c r="F448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -9720,8 +8701,6 @@
           <t>Capacity Additions|Electricity|Wind|Offshore</t>
         </is>
       </c>
-      <c r="E449" t="inlineStr"/>
-      <c r="F449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -9742,8 +8721,6 @@
           <t>Capacity Additions|Electricity|Wind|Onshore</t>
         </is>
       </c>
-      <c r="E450" t="inlineStr"/>
-      <c r="F450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -9759,9 +8736,6 @@
           <t>Capacity Additions|Electricity|Hydrogen</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr"/>
-      <c r="E451" t="inlineStr"/>
-      <c r="F451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -9777,9 +8751,6 @@
           <t>Capacity Additions|Electricity|Storage|Battery ESS</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
-      <c r="E452" t="inlineStr"/>
-      <c r="F452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -9795,9 +8766,6 @@
           <t>Capacity Additions|Electricity|Storage|PSH</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr"/>
-      <c r="E453" t="inlineStr"/>
-      <c r="F453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -9813,9 +8781,6 @@
           <t>Capacity Additions|Electricity|Storage|Hydrogen</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr"/>
-      <c r="E454" t="inlineStr"/>
-      <c r="F454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -9831,9 +8796,6 @@
           <t>Capacity Additions|Hydrogen|Domestic</t>
         </is>
       </c>
-      <c r="D455" t="inlineStr"/>
-      <c r="E455" t="inlineStr"/>
-      <c r="F455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -9849,9 +8811,6 @@
           <t>Capacity Additions|Hydrogen|Domestic|Coal|w/ CCS</t>
         </is>
       </c>
-      <c r="D456" t="inlineStr"/>
-      <c r="E456" t="inlineStr"/>
-      <c r="F456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -9867,9 +8826,6 @@
           <t>Capacity Additions|Hydrogen|Domestic|Coal|w/o CCS</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
-      <c r="E457" t="inlineStr"/>
-      <c r="F457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -9885,9 +8841,6 @@
           <t>Capacity Additions|Hydrogen|Domestic|Biomass</t>
         </is>
       </c>
-      <c r="D458" t="inlineStr"/>
-      <c r="E458" t="inlineStr"/>
-      <c r="F458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -9903,9 +8856,6 @@
           <t>Capacity Additions|Hydrogen|Domestic|Gas|w/ CCS</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr"/>
-      <c r="E459" t="inlineStr"/>
-      <c r="F459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -9921,9 +8871,6 @@
           <t>Capacity Additions|Hydrogen|Domestic|Gas|w/o CCS</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
-      <c r="E460" t="inlineStr"/>
-      <c r="F460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -9939,9 +8886,6 @@
           <t>Capacity Additions|Hydrogen|Domestic|Electricity</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr"/>
-      <c r="E461" t="inlineStr"/>
-      <c r="F461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -9962,8 +8906,6 @@
           <t>Price|Carbon</t>
         </is>
       </c>
-      <c r="E462" t="inlineStr"/>
-      <c r="F462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -9979,9 +8921,6 @@
           <t>Total System Cost|Discounted</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr"/>
-      <c r="E463" t="inlineStr"/>
-      <c r="F463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -9997,9 +8936,6 @@
           <t>Total System Cost|Undiscounted</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr"/>
-      <c r="E464" t="inlineStr"/>
-      <c r="F464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -10020,8 +8956,6 @@
           <t>Investment|Energy Supply|Electricity</t>
         </is>
       </c>
-      <c r="E465" t="inlineStr"/>
-      <c r="F465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -10042,8 +8976,6 @@
           <t>Investment|Energy Supply|Electricity|Biomass|w/ CCS</t>
         </is>
       </c>
-      <c r="E466" t="inlineStr"/>
-      <c r="F466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -10064,8 +8996,6 @@
           <t>Investment|Energy Supply|Electricity|Biomass|w/o CCS</t>
         </is>
       </c>
-      <c r="E467" t="inlineStr"/>
-      <c r="F467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -10081,9 +9011,6 @@
           <t>Investment|Energy Supply|Electricity|Coal|w/ CCS</t>
         </is>
       </c>
-      <c r="D468" t="inlineStr"/>
-      <c r="E468" t="inlineStr"/>
-      <c r="F468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -10099,9 +9026,6 @@
           <t>Investment|Energy Supply|Electricity|Coal|w/o CCS</t>
         </is>
       </c>
-      <c r="D469" t="inlineStr"/>
-      <c r="E469" t="inlineStr"/>
-      <c r="F469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -10122,8 +9046,6 @@
           <t>Investment|Energy Supply|Electricity|Gas|w/ CCS</t>
         </is>
       </c>
-      <c r="E470" t="inlineStr"/>
-      <c r="F470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -10144,8 +9066,6 @@
           <t>Investment|Energy Supply|Electricity|Gas|w/o CCS</t>
         </is>
       </c>
-      <c r="E471" t="inlineStr"/>
-      <c r="F471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -10161,9 +9081,6 @@
           <t>Investment|Energy Supply|Electricity|Hydro</t>
         </is>
       </c>
-      <c r="D472" t="inlineStr"/>
-      <c r="E472" t="inlineStr"/>
-      <c r="F472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -10184,8 +9101,6 @@
           <t>Investment|Energy Supply|Electricity|Nuclear</t>
         </is>
       </c>
-      <c r="E473" t="inlineStr"/>
-      <c r="F473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -10201,9 +9116,6 @@
           <t>Investment|Energy Supply|Electricity|Oil|w/ CCS</t>
         </is>
       </c>
-      <c r="D474" t="inlineStr"/>
-      <c r="E474" t="inlineStr"/>
-      <c r="F474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -10219,9 +9131,6 @@
           <t>Investment|Energy Supply|Electricity|Oil|w/o CCS</t>
         </is>
       </c>
-      <c r="D475" t="inlineStr"/>
-      <c r="E475" t="inlineStr"/>
-      <c r="F475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -10237,9 +9146,6 @@
           <t>Investment|Energy Supply|Electricity|Solar|CSP</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
-      <c r="E476" t="inlineStr"/>
-      <c r="F476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -10260,8 +9166,6 @@
           <t>Investment|Energy Supply|Electricity|Solar|PV</t>
         </is>
       </c>
-      <c r="E477" t="inlineStr"/>
-      <c r="F477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -10282,8 +9186,6 @@
           <t>Investment|Energy Supply|Electricity|Wind|Offshore</t>
         </is>
       </c>
-      <c r="E478" t="inlineStr"/>
-      <c r="F478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -10304,8 +9206,6 @@
           <t>Investment|Energy Supply|Electricity|Wind|Onshore</t>
         </is>
       </c>
-      <c r="E479" t="inlineStr"/>
-      <c r="F479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -10321,9 +9221,6 @@
           <t>Investment|Energy Supply|Electricity|Hydrogen</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr"/>
-      <c r="E480" t="inlineStr"/>
-      <c r="F480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -10339,9 +9236,6 @@
           <t>Investment|Energy Supply|Electricity|Storage|Battery ESS</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr"/>
-      <c r="E481" t="inlineStr"/>
-      <c r="F481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -10357,9 +9251,6 @@
           <t>Investment|Energy Supply|Electricity|Storage|PSH</t>
         </is>
       </c>
-      <c r="D482" t="inlineStr"/>
-      <c r="E482" t="inlineStr"/>
-      <c r="F482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -10375,9 +9266,6 @@
           <t>Investment|Energy Supply|Electricity|Storage|Hydrogen</t>
         </is>
       </c>
-      <c r="D483" t="inlineStr"/>
-      <c r="E483" t="inlineStr"/>
-      <c r="F483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -10393,9 +9281,6 @@
           <t>Investment|Energy Supply|Electricity|Transmission and Distribution</t>
         </is>
       </c>
-      <c r="D484" t="inlineStr"/>
-      <c r="E484" t="inlineStr"/>
-      <c r="F484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -10411,9 +9296,6 @@
           <t>Investment|Hydrogen|Domestic</t>
         </is>
       </c>
-      <c r="D485" t="inlineStr"/>
-      <c r="E485" t="inlineStr"/>
-      <c r="F485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -10429,9 +9311,6 @@
           <t>Investment|Hydrogen|Domestic|Coal|w/ CCS</t>
         </is>
       </c>
-      <c r="D486" t="inlineStr"/>
-      <c r="E486" t="inlineStr"/>
-      <c r="F486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -10447,9 +9326,6 @@
           <t>Investment|Hydrogen|Domestic|Coal|w/o CCS</t>
         </is>
       </c>
-      <c r="D487" t="inlineStr"/>
-      <c r="E487" t="inlineStr"/>
-      <c r="F487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -10465,9 +9341,6 @@
           <t>Investment|Hydrogen|Domestic|Biomass</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr"/>
-      <c r="E488" t="inlineStr"/>
-      <c r="F488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -10483,9 +9356,6 @@
           <t>Investment|Hydrogen|Domestic|Gas|w/ CCS</t>
         </is>
       </c>
-      <c r="D489" t="inlineStr"/>
-      <c r="E489" t="inlineStr"/>
-      <c r="F489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -10501,9 +9371,6 @@
           <t>Investment|Hydrogen|Domestic|Gas|w/o CCS</t>
         </is>
       </c>
-      <c r="D490" t="inlineStr"/>
-      <c r="E490" t="inlineStr"/>
-      <c r="F490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -10519,9 +9386,6 @@
           <t>Investment|Hydrogen|Domestic|Electricity</t>
         </is>
       </c>
-      <c r="D491" t="inlineStr"/>
-      <c r="E491" t="inlineStr"/>
-      <c r="F491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -10542,8 +9406,6 @@
           <t>GDP|MER</t>
         </is>
       </c>
-      <c r="E492" t="inlineStr"/>
-      <c r="F492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -10559,9 +9421,6 @@
           <t>Interest Rate</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr"/>
-      <c r="E493" t="inlineStr"/>
-      <c r="F493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -10582,8 +9441,6 @@
           <t>Population</t>
         </is>
       </c>
-      <c r="E494" t="inlineStr"/>
-      <c r="F494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -10599,9 +9456,6 @@
           <t>Import Price|Primary Energy|Coal</t>
         </is>
       </c>
-      <c r="D495" t="inlineStr"/>
-      <c r="E495" t="inlineStr"/>
-      <c r="F495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -10617,9 +9471,6 @@
           <t>Import Price|Primary Energy|Gas</t>
         </is>
       </c>
-      <c r="D496" t="inlineStr"/>
-      <c r="E496" t="inlineStr"/>
-      <c r="F496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -10635,9 +9486,6 @@
           <t>Import Price|Primary Energy|Oil</t>
         </is>
       </c>
-      <c r="D497" t="inlineStr"/>
-      <c r="E497" t="inlineStr"/>
-      <c r="F497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -10653,9 +9501,6 @@
           <t>Import Price|Primary Energy|Uranium</t>
         </is>
       </c>
-      <c r="D498" t="inlineStr"/>
-      <c r="E498" t="inlineStr"/>
-      <c r="F498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -10671,9 +9516,6 @@
           <t>Import Price|Final|Hydrogen</t>
         </is>
       </c>
-      <c r="D499" t="inlineStr"/>
-      <c r="E499" t="inlineStr"/>
-      <c r="F499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -10689,9 +9531,6 @@
           <t>Import Price|Final|Biomass|Solid</t>
         </is>
       </c>
-      <c r="D500" t="inlineStr"/>
-      <c r="E500" t="inlineStr"/>
-      <c r="F500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -10707,9 +9546,6 @@
           <t>Import Price|Final|Biomass|Liquid</t>
         </is>
       </c>
-      <c r="D501" t="inlineStr"/>
-      <c r="E501" t="inlineStr"/>
-      <c r="F501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -10730,8 +9566,6 @@
           <t>Capital Cost|Electricity|Biomass|w/ CCS</t>
         </is>
       </c>
-      <c r="E502" t="inlineStr"/>
-      <c r="F502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -10752,8 +9586,6 @@
           <t>Capital Cost|Electricity|Biomass|w/o CCS</t>
         </is>
       </c>
-      <c r="E503" t="inlineStr"/>
-      <c r="F503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -10774,8 +9606,6 @@
           <t>Capital Cost|Electricity|Coal|w/ CCS</t>
         </is>
       </c>
-      <c r="E504" t="inlineStr"/>
-      <c r="F504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -10796,8 +9626,6 @@
           <t>Capital Cost|Electricity|Coal|w/o CCS</t>
         </is>
       </c>
-      <c r="E505" t="inlineStr"/>
-      <c r="F505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -10818,8 +9646,6 @@
           <t>Capital Cost|Electricity|Gas|w/ CCS</t>
         </is>
       </c>
-      <c r="E506" t="inlineStr"/>
-      <c r="F506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -10840,8 +9666,6 @@
           <t>Capital Cost|Electricity|Gas|w/o CCS</t>
         </is>
       </c>
-      <c r="E507" t="inlineStr"/>
-      <c r="F507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -10857,9 +9681,6 @@
           <t>Capital Cost|Electricity|Hydro</t>
         </is>
       </c>
-      <c r="D508" t="inlineStr"/>
-      <c r="E508" t="inlineStr"/>
-      <c r="F508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -10880,8 +9701,6 @@
           <t>Capital Cost|Electricity|Nuclear</t>
         </is>
       </c>
-      <c r="E509" t="inlineStr"/>
-      <c r="F509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -10902,8 +9721,6 @@
           <t>Capital Cost|Electricity|Oil|w/ CCS</t>
         </is>
       </c>
-      <c r="E510" t="inlineStr"/>
-      <c r="F510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -10924,8 +9741,6 @@
           <t>Capital Cost|Electricity|Oil|w/o CCS</t>
         </is>
       </c>
-      <c r="E511" t="inlineStr"/>
-      <c r="F511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -10946,8 +9761,6 @@
           <t>Capital Cost|Electricity|Solar|CSP</t>
         </is>
       </c>
-      <c r="E512" t="inlineStr"/>
-      <c r="F512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -10968,8 +9781,6 @@
           <t>Capital Cost|Electricity|Solar|PV</t>
         </is>
       </c>
-      <c r="E513" t="inlineStr"/>
-      <c r="F513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -10990,8 +9801,6 @@
           <t>Capital Cost|Electricity|Wind|Offshore</t>
         </is>
       </c>
-      <c r="E514" t="inlineStr"/>
-      <c r="F514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -11012,8 +9821,6 @@
           <t>Capital Cost|Electricity|Wind|Onshore</t>
         </is>
       </c>
-      <c r="E515" t="inlineStr"/>
-      <c r="F515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -11029,9 +9836,6 @@
           <t>Capital Cost|Electricity|Hydrogen</t>
         </is>
       </c>
-      <c r="D516" t="inlineStr"/>
-      <c r="E516" t="inlineStr"/>
-      <c r="F516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -11047,9 +9851,6 @@
           <t>Capital Cost|Electricity|Storage|Battery ESS</t>
         </is>
       </c>
-      <c r="D517" t="inlineStr"/>
-      <c r="E517" t="inlineStr"/>
-      <c r="F517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -11065,9 +9866,6 @@
           <t>Capital Cost|Electricity|Storage|PSH</t>
         </is>
       </c>
-      <c r="D518" t="inlineStr"/>
-      <c r="E518" t="inlineStr"/>
-      <c r="F518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -11083,9 +9881,6 @@
           <t>Capital Cost|Electricity|Storage|Hydrogen</t>
         </is>
       </c>
-      <c r="D519" t="inlineStr"/>
-      <c r="E519" t="inlineStr"/>
-      <c r="F519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -11101,9 +9896,6 @@
           <t>Capital Cost|Hydrogen|Domestic|Coal|w/ CCS</t>
         </is>
       </c>
-      <c r="D520" t="inlineStr"/>
-      <c r="E520" t="inlineStr"/>
-      <c r="F520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -11119,9 +9911,6 @@
           <t>Capital Cost|Hydrogen|Domestic|Coal|w/o CCS</t>
         </is>
       </c>
-      <c r="D521" t="inlineStr"/>
-      <c r="E521" t="inlineStr"/>
-      <c r="F521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -11137,9 +9926,6 @@
           <t>Capital Cost|Hydrogen|Domestic|Biomass</t>
         </is>
       </c>
-      <c r="D522" t="inlineStr"/>
-      <c r="E522" t="inlineStr"/>
-      <c r="F522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -11155,9 +9941,6 @@
           <t>Capital Cost|Hydrogen|Domestic|Gas|w/ CCS</t>
         </is>
       </c>
-      <c r="D523" t="inlineStr"/>
-      <c r="E523" t="inlineStr"/>
-      <c r="F523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -11173,9 +9956,6 @@
           <t>Capital Cost|Hydrogen|Domestic|Gas|w/o CCS</t>
         </is>
       </c>
-      <c r="D524" t="inlineStr"/>
-      <c r="E524" t="inlineStr"/>
-      <c r="F524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -11191,9 +9971,6 @@
           <t>Capital Cost|Hydrogen|Domestic|Electricity</t>
         </is>
       </c>
-      <c r="D525" t="inlineStr"/>
-      <c r="E525" t="inlineStr"/>
-      <c r="F525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -11209,9 +9986,6 @@
           <t>OM Cost|Fixed|Electricity|Biomass|w/ CCS</t>
         </is>
       </c>
-      <c r="D526" t="inlineStr"/>
-      <c r="E526" t="inlineStr"/>
-      <c r="F526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -11227,9 +10001,6 @@
           <t>OM Cost|Fixed|Electricity|Biomass|w/o CCS</t>
         </is>
       </c>
-      <c r="D527" t="inlineStr"/>
-      <c r="E527" t="inlineStr"/>
-      <c r="F527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -11245,9 +10016,6 @@
           <t>OM Cost|Fixed|Electricity|Coal|w/ CCS</t>
         </is>
       </c>
-      <c r="D528" t="inlineStr"/>
-      <c r="E528" t="inlineStr"/>
-      <c r="F528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -11263,9 +10031,6 @@
           <t>OM Cost|Fixed|Electricity|Coal|w/o CCS</t>
         </is>
       </c>
-      <c r="D529" t="inlineStr"/>
-      <c r="E529" t="inlineStr"/>
-      <c r="F529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -11281,9 +10046,6 @@
           <t>OM Cost|Fixed|Electricity|Gas|w/ CCS</t>
         </is>
       </c>
-      <c r="D530" t="inlineStr"/>
-      <c r="E530" t="inlineStr"/>
-      <c r="F530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -11299,9 +10061,6 @@
           <t>OM Cost|Fixed|Electricity|Gas|w/o CCS</t>
         </is>
       </c>
-      <c r="D531" t="inlineStr"/>
-      <c r="E531" t="inlineStr"/>
-      <c r="F531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -11317,9 +10076,6 @@
           <t>OM Cost|Fixed|Electricity|Hydro</t>
         </is>
       </c>
-      <c r="D532" t="inlineStr"/>
-      <c r="E532" t="inlineStr"/>
-      <c r="F532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -11335,9 +10091,6 @@
           <t>OM Cost|Fixed|Electricity|Nuclear</t>
         </is>
       </c>
-      <c r="D533" t="inlineStr"/>
-      <c r="E533" t="inlineStr"/>
-      <c r="F533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -11353,9 +10106,6 @@
           <t>OM Cost|Fixed|Electricity|Oil|w/ CCS</t>
         </is>
       </c>
-      <c r="D534" t="inlineStr"/>
-      <c r="E534" t="inlineStr"/>
-      <c r="F534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -11371,9 +10121,6 @@
           <t>OM Cost|Fixed|Electricity|OIl|w/o CCS</t>
         </is>
       </c>
-      <c r="D535" t="inlineStr"/>
-      <c r="E535" t="inlineStr"/>
-      <c r="F535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -11389,9 +10136,6 @@
           <t>OM Cost|Fixed|Electricity|Solar|CSP</t>
         </is>
       </c>
-      <c r="D536" t="inlineStr"/>
-      <c r="E536" t="inlineStr"/>
-      <c r="F536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -11407,9 +10151,6 @@
           <t>OM Cost|Fixed|Electricity|Solar|PV</t>
         </is>
       </c>
-      <c r="D537" t="inlineStr"/>
-      <c r="E537" t="inlineStr"/>
-      <c r="F537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -11425,9 +10166,6 @@
           <t>OM Cost|Fixed|Electricity|Wind|Offshore</t>
         </is>
       </c>
-      <c r="D538" t="inlineStr"/>
-      <c r="E538" t="inlineStr"/>
-      <c r="F538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -11443,9 +10181,6 @@
           <t>OM Cost|Fixed|Electricity|Wind|Onshore</t>
         </is>
       </c>
-      <c r="D539" t="inlineStr"/>
-      <c r="E539" t="inlineStr"/>
-      <c r="F539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -11461,9 +10196,6 @@
           <t>OM Cost|Fixed|Electricity|Hydrogen</t>
         </is>
       </c>
-      <c r="D540" t="inlineStr"/>
-      <c r="E540" t="inlineStr"/>
-      <c r="F540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -11479,9 +10211,6 @@
           <t>OM Cost|Fixed|Electricity|Storage|Battery ESS</t>
         </is>
       </c>
-      <c r="D541" t="inlineStr"/>
-      <c r="E541" t="inlineStr"/>
-      <c r="F541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -11497,9 +10226,6 @@
           <t>OM Cost|Fixed|Electricity|Storage|PSH</t>
         </is>
       </c>
-      <c r="D542" t="inlineStr"/>
-      <c r="E542" t="inlineStr"/>
-      <c r="F542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -11515,9 +10241,6 @@
           <t>OM Cost|Fixed|Electricity|Storage|Hydrogen</t>
         </is>
       </c>
-      <c r="D543" t="inlineStr"/>
-      <c r="E543" t="inlineStr"/>
-      <c r="F543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -11533,9 +10256,6 @@
           <t>OM Cost|Fixed|Hydrogen|Domestic|Coal|w/ CCS</t>
         </is>
       </c>
-      <c r="D544" t="inlineStr"/>
-      <c r="E544" t="inlineStr"/>
-      <c r="F544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -11551,9 +10271,6 @@
           <t>OM Cost|Fixed|Hydrogen|Domestic|Coal|w/o CCS</t>
         </is>
       </c>
-      <c r="D545" t="inlineStr"/>
-      <c r="E545" t="inlineStr"/>
-      <c r="F545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -11569,9 +10286,6 @@
           <t>OM Cost|Fixed|Hydrogen|Domestic|Biomass</t>
         </is>
       </c>
-      <c r="D546" t="inlineStr"/>
-      <c r="E546" t="inlineStr"/>
-      <c r="F546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -11587,9 +10301,6 @@
           <t>OM Cost|Fixed|Hydrogen|Domestic|Gas|w/ CCS</t>
         </is>
       </c>
-      <c r="D547" t="inlineStr"/>
-      <c r="E547" t="inlineStr"/>
-      <c r="F547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -11605,9 +10316,6 @@
           <t>OM Cost|Fixed|Hydrogen|Domestic|Gas|w/o CCS</t>
         </is>
       </c>
-      <c r="D548" t="inlineStr"/>
-      <c r="E548" t="inlineStr"/>
-      <c r="F548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -11623,9 +10331,6 @@
           <t>OM Cost|Fixed|Hydrogen|Domestic|Electricity</t>
         </is>
       </c>
-      <c r="D549" t="inlineStr"/>
-      <c r="E549" t="inlineStr"/>
-      <c r="F549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -11641,9 +10346,6 @@
           <t>OM Cost|Variable|Electricity|Biomass|w/ CCS</t>
         </is>
       </c>
-      <c r="D550" t="inlineStr"/>
-      <c r="E550" t="inlineStr"/>
-      <c r="F550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -11659,9 +10361,6 @@
           <t>OM Cost|Variable|Electricity|Biomass|w/o CCS</t>
         </is>
       </c>
-      <c r="D551" t="inlineStr"/>
-      <c r="E551" t="inlineStr"/>
-      <c r="F551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -11677,9 +10376,6 @@
           <t>OM Cost|Variable|Electricity|Coal|w/ CCS</t>
         </is>
       </c>
-      <c r="D552" t="inlineStr"/>
-      <c r="E552" t="inlineStr"/>
-      <c r="F552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -11695,9 +10391,6 @@
           <t>OM Cost|Variable|Electricity|Coal|w/o CCS</t>
         </is>
       </c>
-      <c r="D553" t="inlineStr"/>
-      <c r="E553" t="inlineStr"/>
-      <c r="F553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -11713,9 +10406,6 @@
           <t>OM Cost|Variable|Electricity|Gas|w/ CCS</t>
         </is>
       </c>
-      <c r="D554" t="inlineStr"/>
-      <c r="E554" t="inlineStr"/>
-      <c r="F554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -11731,9 +10421,6 @@
           <t>OM Cost|Variable|Electricity|Gas|w/o CCS</t>
         </is>
       </c>
-      <c r="D555" t="inlineStr"/>
-      <c r="E555" t="inlineStr"/>
-      <c r="F555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -11749,9 +10436,6 @@
           <t>OM Cost|Variable|Electricity|Hydro</t>
         </is>
       </c>
-      <c r="D556" t="inlineStr"/>
-      <c r="E556" t="inlineStr"/>
-      <c r="F556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -11767,9 +10451,6 @@
           <t>OM Cost|Variable|Electricity|Nuclear</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr"/>
-      <c r="E557" t="inlineStr"/>
-      <c r="F557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -11785,9 +10466,6 @@
           <t>OM Cost|Variable|Electricity|Oil|w/ CCS</t>
         </is>
       </c>
-      <c r="D558" t="inlineStr"/>
-      <c r="E558" t="inlineStr"/>
-      <c r="F558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -11803,9 +10481,6 @@
           <t>OM Cost|Variable|Electricity|OIl|w/o CCS</t>
         </is>
       </c>
-      <c r="D559" t="inlineStr"/>
-      <c r="E559" t="inlineStr"/>
-      <c r="F559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -11821,9 +10496,6 @@
           <t>OM Cost|Variable|Electricity|Solar|CSP</t>
         </is>
       </c>
-      <c r="D560" t="inlineStr"/>
-      <c r="E560" t="inlineStr"/>
-      <c r="F560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -11839,9 +10511,6 @@
           <t>OM Cost|Variable|Electricity|Solar|PV</t>
         </is>
       </c>
-      <c r="D561" t="inlineStr"/>
-      <c r="E561" t="inlineStr"/>
-      <c r="F561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -11857,9 +10526,6 @@
           <t>OM Cost|Variable|Electricity|Wind|Offshore</t>
         </is>
       </c>
-      <c r="D562" t="inlineStr"/>
-      <c r="E562" t="inlineStr"/>
-      <c r="F562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -11875,9 +10541,6 @@
           <t>OM Cost|Variable|Electricity|Wind|Onshore</t>
         </is>
       </c>
-      <c r="D563" t="inlineStr"/>
-      <c r="E563" t="inlineStr"/>
-      <c r="F563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -11893,9 +10556,6 @@
           <t>OM Cost|Variable|Electricity|Hydrogen</t>
         </is>
       </c>
-      <c r="D564" t="inlineStr"/>
-      <c r="E564" t="inlineStr"/>
-      <c r="F564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -11911,9 +10571,6 @@
           <t>OM Cost|Variable|Electricity|Storage|Battery ESS</t>
         </is>
       </c>
-      <c r="D565" t="inlineStr"/>
-      <c r="E565" t="inlineStr"/>
-      <c r="F565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -11929,9 +10586,6 @@
           <t>OM Cost|Variable|Electricity|Storage|PSH</t>
         </is>
       </c>
-      <c r="D566" t="inlineStr"/>
-      <c r="E566" t="inlineStr"/>
-      <c r="F566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -11947,9 +10601,6 @@
           <t>OM Cost|Variable|Electricity|Storage|Hydrogen</t>
         </is>
       </c>
-      <c r="D567" t="inlineStr"/>
-      <c r="E567" t="inlineStr"/>
-      <c r="F567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -11965,9 +10616,6 @@
           <t>OM Cost|Variable|Hydrogen|Domestic|Coal|w/ CCS</t>
         </is>
       </c>
-      <c r="D568" t="inlineStr"/>
-      <c r="E568" t="inlineStr"/>
-      <c r="F568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -11983,9 +10631,6 @@
           <t>OM Cost|Variable|Hydrogen|Domestic|Coal|w/o CCS</t>
         </is>
       </c>
-      <c r="D569" t="inlineStr"/>
-      <c r="E569" t="inlineStr"/>
-      <c r="F569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -12001,9 +10646,6 @@
           <t>OM Cost|Variable|Hydrogen|Domestic|Biomass</t>
         </is>
       </c>
-      <c r="D570" t="inlineStr"/>
-      <c r="E570" t="inlineStr"/>
-      <c r="F570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -12019,9 +10661,6 @@
           <t>OM Cost|Variable|Hydrogen|Domestic|Gas|w/ CCS</t>
         </is>
       </c>
-      <c r="D571" t="inlineStr"/>
-      <c r="E571" t="inlineStr"/>
-      <c r="F571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -12037,9 +10676,6 @@
           <t>OM Cost|Variable|Hydrogen|Domestic|Gas|w/o CCS</t>
         </is>
       </c>
-      <c r="D572" t="inlineStr"/>
-      <c r="E572" t="inlineStr"/>
-      <c r="F572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -12055,9 +10691,6 @@
           <t>OM Cost|Variable|Hydrogen|Domestic|Electricity</t>
         </is>
       </c>
-      <c r="D573" t="inlineStr"/>
-      <c r="E573" t="inlineStr"/>
-      <c r="F573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -12083,7 +10716,6 @@
           <t>Production|Iron and Steel|Iron</t>
         </is>
       </c>
-      <c r="F574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -12104,8 +10736,6 @@
           <t>Production|Iron and Steel|Steel</t>
         </is>
       </c>
-      <c r="E575" t="inlineStr"/>
-      <c r="F575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -12121,9 +10751,6 @@
           <t>Production|Iron and Steel|Iron</t>
         </is>
       </c>
-      <c r="D576" t="inlineStr"/>
-      <c r="E576" t="inlineStr"/>
-      <c r="F576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -12139,9 +10766,6 @@
           <t>Production|Iron and Steel|Iron Ore</t>
         </is>
       </c>
-      <c r="D577" t="inlineStr"/>
-      <c r="E577" t="inlineStr"/>
-      <c r="F577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -12162,8 +10786,6 @@
           <t>Production|Non-Metallic Minerals|Cement</t>
         </is>
       </c>
-      <c r="E578" t="inlineStr"/>
-      <c r="F578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -12179,9 +10801,6 @@
           <t>Production|Non-Metallic Minerals|Cement Clinker</t>
         </is>
       </c>
-      <c r="D579" t="inlineStr"/>
-      <c r="E579" t="inlineStr"/>
-      <c r="F579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -12197,9 +10816,6 @@
           <t>Production|Non-Metallic Minerals|Glass</t>
         </is>
       </c>
-      <c r="D580" t="inlineStr"/>
-      <c r="E580" t="inlineStr"/>
-      <c r="F580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -12215,9 +10831,6 @@
           <t>Production|Non-Metallic Minerals|Limestone</t>
         </is>
       </c>
-      <c r="D581" t="inlineStr"/>
-      <c r="E581" t="inlineStr"/>
-      <c r="F581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -12243,7 +10856,6 @@
           <t>Production|Chemicals|Ammonia; Production|Chemicals|Nitrogen Fertilizer</t>
         </is>
       </c>
-      <c r="F582" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -12259,9 +10871,6 @@
           <t>Building|Floor Space|Residential</t>
         </is>
       </c>
-      <c r="D583" t="inlineStr"/>
-      <c r="E583" t="inlineStr"/>
-      <c r="F583" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -12277,9 +10886,6 @@
           <t>Building|Floor Space|Commercial/Public</t>
         </is>
       </c>
-      <c r="D584" t="inlineStr"/>
-      <c r="E584" t="inlineStr"/>
-      <c r="F584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -12295,9 +10901,6 @@
           <t>Final Energy|Transportation|Hydrogen|International Shipping</t>
         </is>
       </c>
-      <c r="D585" t="inlineStr"/>
-      <c r="E585" t="inlineStr"/>
-      <c r="F585" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/kaist/kmip/template/kmip_gcam_mapping_template.xlsx
+++ b/kaist/kmip/template/kmip_gcam_mapping_template.xlsx
@@ -3108,7 +3108,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Secondary Energy|Hydrogen|Other; Secondary Energy|Hydrogen|Import</t>
+          <t>Secondary Energy|Hydrogen|Import</t>
         </is>
       </c>
     </row>
@@ -3131,11 +3131,6 @@
           <t>Secondary Energy|Hydrogen</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Secondary Energy|Hydrogen|Other</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3264,6 +3259,11 @@
       <c r="D152" t="inlineStr">
         <is>
           <t>Secondary Energy|Hydrogen|Electricity</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Secondary Energy|Hydrogen|Other</t>
         </is>
       </c>
     </row>
